--- a/WorkBot/refactor/data/orders/Equal Exchange/Equal Exchange_Triphammer_2025-10-16.xlsx
+++ b/WorkBot/refactor/data/orders/Equal Exchange/Equal Exchange_Triphammer_2025-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,52 +446,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equal Exchange - Black Silk Espresso</t>
+          <t>Equal Exchange - Breakfast Blend, Decaf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77.50</t>
+          <t>106.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>387.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Equal Exchange - Breakfast Blend, Decaf</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>318.00</t>
         </is>
